--- a/output/laminas_comunales/comunal_s_isapre_a_2022_biobio.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2022_biobio.xlsx
@@ -375,46 +375,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>San Pedro de la Paz</t>
         </is>
       </c>
       <c r="C2">
-        <v>48511</v>
+        <v>23.09907458993264</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>San Pedro de la Paz</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="C3">
-        <v>31925</v>
+        <v>21.06005747874936</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Chiguayante</t>
         </is>
       </c>
       <c r="C4">
-        <v>23914</v>
+        <v>17.16389601695861</v>
       </c>
     </row>
     <row r="5">
@@ -429,22 +429,22 @@
         </is>
       </c>
       <c r="C5">
-        <v>19376</v>
+        <v>12.3522586732287</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chiguayante</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C6">
-        <v>15384</v>
+        <v>10.58895939142486</v>
       </c>
     </row>
     <row r="7">
@@ -459,382 +459,382 @@
         </is>
       </c>
       <c r="C7">
-        <v>8978</v>
+        <v>9.691591912518756</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Coronel</t>
+          <t>Laja</t>
         </is>
       </c>
       <c r="C8">
-        <v>7016</v>
+        <v>7.983740479103359</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tomé</t>
+          <t>Arauco</t>
         </is>
       </c>
       <c r="C9">
-        <v>3749</v>
+        <v>7.396261062511158</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Penco</t>
+          <t>Nacimiento</t>
         </is>
       </c>
       <c r="C10">
-        <v>3278</v>
+        <v>6.71876115036038</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8107</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arauco</t>
+          <t>Penco</t>
         </is>
       </c>
       <c r="C11">
-        <v>2900</v>
+        <v>6.493403589398201</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Laja</t>
+          <t>Tomé</t>
         </is>
       </c>
       <c r="C12">
-        <v>2023</v>
+        <v>6.238767223590495</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nacimiento</t>
+          <t>San Rosendo</t>
         </is>
       </c>
       <c r="C13">
-        <v>1883</v>
+        <v>5.617691916624301</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cabrero</t>
+          <t>Coronel</t>
         </is>
       </c>
       <c r="C14">
-        <v>1636</v>
+        <v>5.601328479274446</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lota</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="C15">
-        <v>1381</v>
+        <v>5.363798411926754</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hualqui</t>
+          <t>Cabrero</t>
         </is>
       </c>
       <c r="C16">
-        <v>1236</v>
+        <v>4.985828787370859</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8312</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mulchén</t>
+          <t>Tucapel</t>
         </is>
       </c>
       <c r="C17">
-        <v>1202</v>
+        <v>4.79272345635823</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cañete</t>
+          <t>Santa Juana</t>
         </is>
       </c>
       <c r="C18">
-        <v>1195</v>
+        <v>4.52113268802982</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Yumbel</t>
+          <t>Hualqui</t>
         </is>
       </c>
       <c r="C19">
-        <v>989</v>
+        <v>4.496180429246999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
+          <t>Negrete</t>
         </is>
       </c>
       <c r="C20">
-        <v>921</v>
+        <v>4.376133179495632</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tucapel</t>
+          <t>Antuco</t>
         </is>
       </c>
       <c r="C21">
-        <v>822</v>
+        <v>4.305818105440034</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Santa Juana</t>
+          <t>Yumbel</t>
         </is>
       </c>
       <c r="C22">
-        <v>752</v>
+        <v>4.078014184397163</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lebu</t>
+          <t>Mulchén</t>
         </is>
       </c>
       <c r="C23">
-        <v>719</v>
+        <v>3.738259625552031</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Cañete</t>
         </is>
       </c>
       <c r="C24">
-        <v>662</v>
+        <v>3.265473425331329</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Los Alamos</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="C25">
-        <v>633</v>
+        <v>3.190736571244773</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8307</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Negrete</t>
+          <t>Lota</t>
         </is>
       </c>
       <c r="C26">
-        <v>531</v>
+        <v>2.898520306432994</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Contulmo</t>
         </is>
       </c>
       <c r="C27">
-        <v>496</v>
+        <v>2.831551574689396</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8309</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Quilleco</t>
+          <t>Quilaco</t>
         </is>
       </c>
       <c r="C28">
-        <v>279</v>
+        <v>2.737345209645883</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>San Rosendo</t>
+          <t>Quilleco</t>
         </is>
       </c>
       <c r="C29">
-        <v>221</v>
+        <v>2.674976030680729</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8302</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Antuco</t>
+          <t>Lebu</t>
         </is>
       </c>
       <c r="C30">
-        <v>205</v>
+        <v>2.614260262516817</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Contulmo</t>
+          <t>Curanilahue</t>
         </is>
       </c>
       <c r="C31">
-        <v>196</v>
+        <v>2.603386380981994</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tirúa</t>
+          <t>Los Alamos</t>
         </is>
       </c>
       <c r="C32">
-        <v>166</v>
+        <v>2.550362610797744</v>
       </c>
     </row>
     <row r="33">
@@ -849,22 +849,22 @@
         </is>
       </c>
       <c r="C33">
-        <v>130</v>
+        <v>1.767024602419464</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8308</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Quilaco</t>
+          <t>Tirúa</t>
         </is>
       </c>
       <c r="C34">
-        <v>126</v>
+        <v>1.458699472759227</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +920,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
